--- a/ckanext/lhm/schemas/template_plandb.xlsx
+++ b/ckanext/lhm/schemas/template_plandb.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\home\mb\dev\ckanext-lhm\ckanext\lhm\schemas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\home\mb\p2\ckanext-lhm\ckanext\lhm\schemas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C653A3C-BBA8-4C6C-9DFC-D012012B3AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622777C3-B662-4C82-9DF7-3795BEB4894D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" xr2:uid="{EFAD0BDA-2C19-4F99-80E8-84599936D919}"/>
   </bookViews>
@@ -38,15 +38,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="271">
   <si>
     <t>nein</t>
   </si>
@@ -818,9 +815,6 @@
     <t>HAII_PRIO</t>
   </si>
   <si>
-    <t>INNENSTADT</t>
-  </si>
-  <si>
     <t>LBK</t>
   </si>
   <si>
@@ -854,9 +848,6 @@
     <t>Abteilung *</t>
   </si>
   <si>
-    <t>1.3.6.</t>
-  </si>
-  <si>
     <t>Metadatenschema *</t>
   </si>
   <si>
@@ -867,6 +858,21 @@
   </si>
   <si>
     <t>LHM_MD_metadatenschema</t>
+  </si>
+  <si>
+    <t>WIRT</t>
+  </si>
+  <si>
+    <t>STEP</t>
+  </si>
+  <si>
+    <t>HANDLUNGSRAEUME</t>
+  </si>
+  <si>
+    <t>Kontinuierlich</t>
+  </si>
+  <si>
+    <t>1.3.7.</t>
   </si>
 </sst>
 </file>
@@ -1059,9 +1065,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1080,12 +1085,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1121,10 +1120,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1468,634 +1467,395 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{860E5F97-3212-47C5-A469-BCE2C1CB3CAC}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="48.5" style="14" customWidth="1"/>
-    <col min="2" max="2" width="40.69921875" style="14" customWidth="1"/>
-    <col min="3" max="11" width="11" style="14"/>
-    <col min="12" max="12" width="20.19921875" style="14" customWidth="1"/>
-    <col min="13" max="13" width="36.8984375" style="14" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="29" style="14" customWidth="1"/>
-    <col min="15" max="16384" width="11" style="14"/>
+    <col min="1" max="1" width="48.5" style="11" customWidth="1"/>
+    <col min="2" max="2" width="40.69921875" style="11" customWidth="1"/>
+    <col min="3" max="11" width="11" style="11"/>
+    <col min="12" max="12" width="20.19921875" style="11" customWidth="1"/>
+    <col min="13" max="13" width="36.8984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="29" style="11" customWidth="1"/>
+    <col min="15" max="16384" width="11" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="13" customFormat="1">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="9" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="17"/>
+      <c r="B2" s="16"/>
+      <c r="K2" s="14"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="17"/>
+      <c r="B3" s="16"/>
+      <c r="K3" s="14"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="K4" s="14"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="17"/>
+      <c r="B7" s="16"/>
+      <c r="K7" s="14"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="17"/>
+      <c r="B8" s="16"/>
+      <c r="K8" s="14"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="17"/>
+      <c r="B9" s="16"/>
+      <c r="K9" s="14"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="K10" s="14"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="K11" s="14"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="19"/>
+      <c r="K12" s="14"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="18"/>
+      <c r="K13" s="14"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="B14" s="18"/>
+      <c r="K14" s="14"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="B15" s="18"/>
+      <c r="K15" s="14"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="B16" s="18"/>
+      <c r="K16" s="14"/>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="16"/>
+      <c r="K17" s="14"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="B18" s="16"/>
+      <c r="K18" s="14"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="K19" s="14"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="B20" s="18"/>
+      <c r="K20" s="14"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="B21" s="18"/>
+      <c r="K21" s="14"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="K22" s="14"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="B23" s="18"/>
+      <c r="K23" s="14"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="B24" s="18"/>
+      <c r="K24" s="14"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="K25" s="14"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B26" s="18"/>
+      <c r="K26" s="14"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="B27" s="18"/>
+      <c r="K27" s="14"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="B28" s="18"/>
+      <c r="K28" s="14"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="B29" s="18"/>
+      <c r="K29" s="14"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B30" s="16"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
+      <c r="K30" s="16"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" s="16"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="16"/>
+      <c r="K31" s="16"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="22"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" s="23"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B34" s="23"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="17"/>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="17"/>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="22"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="17"/>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="17"/>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="17"/>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="17"/>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="16" t="s">
-        <v>232</v>
-      </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="17"/>
-    </row>
-    <row r="17" spans="1:12">
-      <c r="A17" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="17"/>
-    </row>
-    <row r="18" spans="1:12">
-      <c r="A18" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="17"/>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" s="19"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="17"/>
-    </row>
-    <row r="20" spans="1:12">
-      <c r="A20" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="B20" s="21"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="17"/>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="A21" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="17"/>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" s="16" t="s">
-        <v>233</v>
-      </c>
-      <c r="B22" s="21"/>
-      <c r="K22" s="17"/>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="B23" s="21"/>
-      <c r="K23" s="17"/>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="B24" s="21"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="17"/>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="B25" s="21"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="17"/>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="B26" s="21"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="17"/>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="17"/>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="17"/>
-    </row>
-    <row r="29" spans="1:12">
-      <c r="A29" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="B29" s="21"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="17"/>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-    </row>
-    <row r="31" spans="1:12">
-      <c r="A31" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="B31" s="19"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="B32" s="25"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-    </row>
-    <row r="33" spans="1:12">
-      <c r="A33" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="B33" s="26"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-    </row>
-    <row r="34" spans="1:12">
-      <c r="A34" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="B34" s="26"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-    </row>
-    <row r="35" spans="1:12">
-      <c r="A35" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="B35" s="26"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
-    </row>
-    <row r="36" spans="1:12">
-      <c r="A36" s="14" t="s">
+      <c r="B35" s="23"/>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="B36" s="26" t="s">
-        <v>263</v>
-      </c>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="12"/>
-    </row>
-    <row r="38" spans="1:12">
-      <c r="A38" s="14" t="s">
+      <c r="B36" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="11" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:12">
-      <c r="A39" s="14" t="s">
+    <row r="39" spans="1:4">
+      <c r="A39" s="11" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="41" spans="1:12">
-      <c r="A41" s="29" t="s">
+    <row r="41" spans="1:4">
+      <c r="A41" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="B41" s="30"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-    </row>
-    <row r="42" spans="1:12">
-      <c r="A42" s="30"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-    </row>
-    <row r="43" spans="1:12">
-      <c r="A43" s="30"/>
-      <c r="B43" s="30"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-    </row>
-    <row r="44" spans="1:12">
-      <c r="A44" s="30"/>
-      <c r="B44" s="30"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-    </row>
-    <row r="45" spans="1:12">
-      <c r="A45" s="30"/>
-      <c r="B45" s="30"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
-    </row>
-    <row r="46" spans="1:12">
-      <c r="A46" s="30"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-    </row>
-    <row r="47" spans="1:12">
-      <c r="A47" s="30"/>
-      <c r="B47" s="30"/>
-      <c r="C47" s="30"/>
-      <c r="D47" s="30"/>
-    </row>
-    <row r="48" spans="1:12">
-      <c r="A48" s="30"/>
-      <c r="B48" s="30"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
+      <c r="B41" s="27"/>
+      <c r="C41" s="27"/>
+      <c r="D41" s="27"/>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="27"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="27"/>
+      <c r="D42" s="27"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="27"/>
+      <c r="B43" s="27"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="27"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="27"/>
+      <c r="B44" s="27"/>
+      <c r="C44" s="27"/>
+      <c r="D44" s="27"/>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="27"/>
+      <c r="B45" s="27"/>
+      <c r="C45" s="27"/>
+      <c r="D45" s="27"/>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="27"/>
+      <c r="B46" s="27"/>
+      <c r="C46" s="27"/>
+      <c r="D46" s="27"/>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="27"/>
+      <c r="B47" s="27"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="27"/>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="27"/>
+      <c r="B48" s="27"/>
+      <c r="C48" s="27"/>
+      <c r="D48" s="27"/>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="30"/>
-      <c r="B49" s="30"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="30"/>
+      <c r="A49" s="27"/>
+      <c r="B49" s="27"/>
+      <c r="C49" s="27"/>
+      <c r="D49" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2153,29 +1913,29 @@
   <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="3" width="20.69921875" style="28" customWidth="1"/>
-    <col min="4" max="5" width="52.69921875" style="28" customWidth="1"/>
-    <col min="6" max="6" width="20.69921875" style="28" customWidth="1"/>
-    <col min="7" max="16384" width="11" style="7"/>
+    <col min="1" max="3" width="20.69921875" style="25" customWidth="1"/>
+    <col min="4" max="5" width="52.69921875" style="25" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" style="25" customWidth="1"/>
+    <col min="7" max="16384" width="11" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="24" t="s">
         <v>182</v>
       </c>
     </row>
@@ -2194,24 +1954,24 @@
   <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="10.69921875" style="28" customWidth="1"/>
-    <col min="2" max="3" width="20.69921875" style="28" customWidth="1"/>
-    <col min="4" max="4" width="136.5" style="28" customWidth="1"/>
-    <col min="5" max="13" width="20.69921875" style="7" customWidth="1"/>
-    <col min="14" max="16384" width="11" style="7"/>
+    <col min="1" max="1" width="10.69921875" style="25" customWidth="1"/>
+    <col min="2" max="3" width="20.69921875" style="25" customWidth="1"/>
+    <col min="4" max="4" width="136.5" style="25" customWidth="1"/>
+    <col min="5" max="13" width="20.69921875" style="6" customWidth="1"/>
+    <col min="14" max="16384" width="11" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="24" t="s">
         <v>226</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="24" t="s">
         <v>227</v>
       </c>
     </row>
@@ -2230,22 +1990,22 @@
   <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="3" width="20.69921875" style="28" customWidth="1"/>
-    <col min="4" max="4" width="126.5" style="28" customWidth="1"/>
-    <col min="5" max="16384" width="11" style="7"/>
+    <col min="1" max="3" width="20.69921875" style="25" customWidth="1"/>
+    <col min="4" max="4" width="126.5" style="25" customWidth="1"/>
+    <col min="5" max="16384" width="11" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="24" t="s">
         <v>183</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="24" t="s">
         <v>100</v>
       </c>
     </row>
@@ -2285,815 +2045,801 @@
     <col min="20" max="20" width="23.796875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="27.3984375" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="18.8984375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.8984375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="19.796875" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="21.796875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="24.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:25">
+      <c r="A1" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="W1" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="X1" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Y1" s="4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="W6" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="A7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="K10" s="12"/>
+      <c r="R10" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="K11" s="12"/>
+      <c r="R11" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="K12" s="12"/>
+      <c r="R12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="K13" s="12"/>
+      <c r="R13" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="K14" s="12"/>
+      <c r="W14" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="K15" s="12"/>
+      <c r="W15" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="K16" s="12"/>
+      <c r="W16" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="K17" s="12"/>
+      <c r="W17" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23">
+      <c r="A18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="K18" s="12"/>
+      <c r="W18" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K19" s="12"/>
+      <c r="W19" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K20" s="12"/>
+      <c r="W20" s="2" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="W2" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="V3" s="2" t="s">
+    <row r="21" spans="1:23">
+      <c r="A21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="K21" s="12"/>
+      <c r="W21" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23">
+      <c r="A22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W22" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="W3" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="W4" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="X4" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y4" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="W5" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="X5" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="U6" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="W6" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="X6" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25">
-      <c r="A7" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="W7" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="X7" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25">
-      <c r="A8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="X8" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25">
-      <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E9" s="1"/>
-      <c r="G9" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="U9" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="X9" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25">
-      <c r="A10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E10" s="1"/>
-      <c r="G10" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="K10" s="15"/>
-      <c r="R10" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="U10" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="W10" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="X10" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25">
-      <c r="A11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E11" s="1"/>
-      <c r="G11" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K11" s="15"/>
-      <c r="R11" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="U11" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="W11" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="X11" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25">
-      <c r="A12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E12" s="1"/>
-      <c r="K12" s="15"/>
-      <c r="R12" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="U12" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25">
-      <c r="A13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E13" s="1"/>
-      <c r="K13" s="15"/>
-      <c r="R13" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="W13" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25">
-      <c r="A14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E14" s="1"/>
-      <c r="K14" s="15"/>
-      <c r="W14" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25">
-      <c r="A15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E15" s="1"/>
-      <c r="K15" s="15"/>
-      <c r="W15" s="3" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25">
-      <c r="A16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E16" s="1"/>
-      <c r="K16" s="15"/>
-      <c r="W16" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23">
-      <c r="A17" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="E17" s="1"/>
-      <c r="K17" s="15"/>
-      <c r="W17" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23">
-      <c r="A18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E18" s="1"/>
-      <c r="K18" s="15"/>
-      <c r="W18" s="3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23">
-      <c r="A19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E19" s="1"/>
-      <c r="K19" s="15"/>
-      <c r="W19" s="3" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23">
-      <c r="A20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E20" s="1"/>
-      <c r="K20" s="15"/>
-      <c r="W20" s="3" t="s">
+    </row>
+    <row r="23" spans="1:23">
+      <c r="A23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="W23" s="2" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
-      <c r="A21" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E21" s="1"/>
-      <c r="K21" s="15"/>
-      <c r="W21" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23">
-      <c r="A22" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E22" s="1"/>
-    </row>
-    <row r="23" spans="1:23">
-      <c r="A23" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E23" s="1"/>
-    </row>
     <row r="24" spans="1:23">
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E24" s="1"/>
     </row>
     <row r="25" spans="1:23">
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E25" s="1"/>
     </row>
     <row r="26" spans="1:23">
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E26" s="1"/>
     </row>
     <row r="27" spans="1:23">
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E27" s="1"/>
     </row>
     <row r="28" spans="1:23">
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E28" s="1"/>
     </row>
     <row r="29" spans="1:23">
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E29" s="1"/>
     </row>
     <row r="30" spans="1:23">
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E30" s="1"/>
     </row>
     <row r="31" spans="1:23">
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E31" s="1"/>
     </row>
     <row r="32" spans="1:23">
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="33" spans="2:2">
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="34" spans="2:2">
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="35" spans="2:2">
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="36" spans="2:2">
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>56</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="KFe0QCuD87thpdz4ck4fKMGzw5Q53fIojp2KlnoFb1hbwe+Rkl3kkRpWu6YGCCD+TcLUYpZIHFUAvwG7q3nsPA==" saltValue="7iA+BZblGrXOgve/UNdGnw==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="XQ0ScWYg5BozhXTL3qD7Ja8vGQVkbfQ5TFCSSURIC86Jv4/h1sqsnzQtrCN2jIc/JaLOX4yoW3a7XLWJ6XSQpA==" saltValue="4n/cAA+cyycyOEXksfwb5A==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/ckanext/lhm/schemas/template_plandb.xlsx
+++ b/ckanext/lhm/schemas/template_plandb.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\home\mb\p2\ckanext-lhm\ckanext\lhm\schemas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622777C3-B662-4C82-9DF7-3795BEB4894D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B142522-A636-46CD-88A5-1A76D2145313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" xr2:uid="{EFAD0BDA-2C19-4F99-80E8-84599936D919}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Datenverzeichnis" sheetId="17" r:id="rId2"/>
     <sheet name="Katalogwerte" sheetId="18" r:id="rId3"/>
     <sheet name="Dienste und Dokumente" sheetId="19" r:id="rId4"/>
-    <sheet name="Wertelisten" sheetId="16" state="hidden" r:id="rId5"/>
+    <sheet name="Wertelisten" sheetId="16" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Metadaten!$A$1:$K$49</definedName>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="273">
   <si>
     <t>nein</t>
   </si>
@@ -873,6 +873,12 @@
   </si>
   <si>
     <t>1.3.7.</t>
+  </si>
+  <si>
+    <t>NCLOB</t>
+  </si>
+  <si>
+    <t>MOBIDAM_MD_update-zyklus</t>
   </si>
 </sst>
 </file>
@@ -2021,7 +2027,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D073E50-F226-4B6A-BC2C-397D6C68AFA7}">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:Y36"/>
+  <dimension ref="A1:Z36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="22.3984375" bestFit="1" customWidth="1"/>
@@ -2048,9 +2054,10 @@
     <col min="23" max="23" width="19.796875" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="21.796875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="24.296875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="25.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:26">
       <c r="A1" s="4" t="s">
         <v>201</v>
       </c>
@@ -2126,8 +2133,11 @@
       <c r="Y1" s="4" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="2" spans="1:25">
+      <c r="Z1" s="4" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2199,8 +2209,11 @@
       <c r="Y2" s="1" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="3" spans="1:25">
+      <c r="Z2" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2271,13 +2284,16 @@
         <v>240</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>269</v>
+        <v>142</v>
       </c>
       <c r="Y3" s="1" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="4" spans="1:25">
+      <c r="Z3" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -2339,13 +2355,16 @@
         <v>241</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Y4" s="1" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="5" spans="1:25">
+      <c r="Z4" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -2386,10 +2405,13 @@
         <v>242</v>
       </c>
       <c r="X5" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="Z5" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:26">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -2430,10 +2452,13 @@
         <v>243</v>
       </c>
       <c r="X6" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="Z6" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:26">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
@@ -2468,10 +2493,13 @@
         <v>244</v>
       </c>
       <c r="X7" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z7" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:26">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -2506,10 +2534,13 @@
         <v>245</v>
       </c>
       <c r="X8" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z8" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:26">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -2532,10 +2563,13 @@
         <v>246</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25">
+        <v>237</v>
+      </c>
+      <c r="Z9" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -2559,10 +2593,10 @@
         <v>247</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -2586,10 +2620,10 @@
         <v>248</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -2609,11 +2643,8 @@
       <c r="W12" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="X12" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25">
+    </row>
+    <row r="13" spans="1:26">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -2627,11 +2658,14 @@
       <c r="R13" s="1" t="s">
         <v>260</v>
       </c>
+      <c r="U13" s="1" t="s">
+        <v>271</v>
+      </c>
       <c r="W13" s="2" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:26">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -2646,7 +2680,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:26">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -2661,7 +2695,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:26">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -2839,7 +2873,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="XQ0ScWYg5BozhXTL3qD7Ja8vGQVkbfQ5TFCSSURIC86Jv4/h1sqsnzQtrCN2jIc/JaLOX4yoW3a7XLWJ6XSQpA==" saltValue="4n/cAA+cyycyOEXksfwb5A==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/ckanext/lhm/schemas/template_plandb.xlsx
+++ b/ckanext/lhm/schemas/template_plandb.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\home\mb\p2\ckanext-lhm\ckanext\lhm\schemas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B142522-A636-46CD-88A5-1A76D2145313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D8B1BD1-42AE-4867-A118-99A200137651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" xr2:uid="{EFAD0BDA-2C19-4F99-80E8-84599936D919}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Datenverzeichnis" sheetId="17" r:id="rId2"/>
     <sheet name="Katalogwerte" sheetId="18" r:id="rId3"/>
     <sheet name="Dienste und Dokumente" sheetId="19" r:id="rId4"/>
-    <sheet name="Wertelisten" sheetId="16" r:id="rId5"/>
+    <sheet name="Wertelisten" sheetId="16" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Metadaten!$A$1:$K$49</definedName>
@@ -1138,14 +1138,14 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1751,7 +1751,7 @@
       <c r="K30" s="16"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="26" t="s">
         <v>102</v>
       </c>
       <c r="B31" s="16"/>
@@ -1808,60 +1808,60 @@
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="26" t="s">
+      <c r="A41" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="B41" s="27"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
+      <c r="B41" s="28"/>
+      <c r="C41" s="28"/>
+      <c r="D41" s="28"/>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="27"/>
-      <c r="B42" s="27"/>
-      <c r="C42" s="27"/>
-      <c r="D42" s="27"/>
+      <c r="A42" s="28"/>
+      <c r="B42" s="28"/>
+      <c r="C42" s="28"/>
+      <c r="D42" s="28"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="27"/>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
+      <c r="A43" s="28"/>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="27"/>
-      <c r="B44" s="27"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="27"/>
+      <c r="A44" s="28"/>
+      <c r="B44" s="28"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="27"/>
-      <c r="B45" s="27"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="27"/>
+      <c r="A45" s="28"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="27"/>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
+      <c r="A46" s="28"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="27"/>
-      <c r="B47" s="27"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
+      <c r="A47" s="28"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="27"/>
-      <c r="B48" s="27"/>
-      <c r="C48" s="27"/>
-      <c r="D48" s="27"/>
+      <c r="A48" s="28"/>
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="27"/>
-      <c r="B49" s="27"/>
-      <c r="C49" s="27"/>
-      <c r="D49" s="27"/>
+      <c r="A49" s="28"/>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2873,7 +2873,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="8QQ9Fz1rKWIVuZr/ZWzSzQH6i7gTJI7J+Z+altx8qjy6Uj9r+JIXmbCMXi/8y+2ivXT+heunTljNGJLAr4ALjw==" saltValue="Q8i4nrkqZWrIPPW1MCJY6w==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
